--- a/business_surveys/029_customer_product_research_survey--business_surveys.xlsx
+++ b/business_surveys/029_customer_product_research_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mr',_'value':_'mr'}</t>
+          <t>mr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Mr', 'value': 'Mr'}</t>
+          <t>Mr</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mrs',_'value':_'mrs'}</t>
+          <t>mrs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mrs', 'value': 'Mrs'}</t>
+          <t>Mrs</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'ms',_'value':_'ms'}</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Ms', 'value': 'Ms'}</t>
+          <t>Ms</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'dr',_'value':_'dr'}</t>
+          <t>dr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Dr', 'value': 'Dr'}</t>
+          <t>Dr</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'apple',_'value':_'apple'}</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Apple', 'value': 'Apple'}</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'microsoft',_'value':_'microsoft'}</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Microsoft', 'value': 'Microsoft'}</t>
+          <t>Microsoft</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'google',_'value':_'google'}</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Google', 'value': 'Google'}</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily', 'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly', 'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely', 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied',_'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied', 'value': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_satisfied',_'value':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Satisfied', 'value': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'yes',_'value':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Yes', 'value': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'no',_'value':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'No', 'value': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
